--- a/АБК/Том СПС АБК/Журнал входного контроля СПС АБК.xlsx
+++ b/АБК/Том СПС АБК/Журнал входного контроля СПС АБК.xlsx
@@ -508,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -576,7 +576,7 @@
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Рабочая документация 16/1/26-АПС,СОУЭ-Р, листы 5, 6; исполнительная документация 16/1/26-ИД-АБК, листы 2–3. Количество материалов — по АОСР № 1-СПС-АБК, 2-СПС-АБК, 3-СПС-АБК; оборудование — по исполнительной документации.</t>
+          <t>Рабочая документация 16/1/26-АПС,СОУЭ-Р, листы 5, 6; исполнительная документация 16/1/26-АПС,СОУЭ-ИД-АБК, листы 2–3. Спецификация 16/1/26-АПС,СОУЭ-ИД-АБК.СО. Количество материалов — по АОСР № 1-СПС-АБК, 2-СПС-АБК, 3-СПС-АБК; оборудование — по исполнительной документации.</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="F20" s="10" t="n">
-        <v>168</v>
+        <v>204</v>
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="F27" s="10" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="F32" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
@@ -1579,12 +1579,12 @@
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Оповещатель пожарный речевой настенный 6/3/1,5 Вт, линия 100 В, ОПР-С106.1 (поз. BIAD)</t>
+          <t>Батарея аккумуляторная 12 В 18 А·ч (в шкафу RFA1), DT 12В 18Ач</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Delta</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="F33" s="10" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
@@ -1632,91 +1632,144 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
+          <t>Оповещатель пожарный речевой настенный 6/3/1,5 Вт, линия 100 В, ОПР-С106.1 (поз. BIAD)</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="G34" s="11" t="inlineStr">
+        <is>
+          <t>Паспорт (руководство по эксплуатации) изготовителя</t>
+        </is>
+      </c>
+      <c r="H34" s="11" t="inlineStr">
+        <is>
+          <t>Внешний осмотр, маркировка, комплектность — без замечаний. Паспорт изготовителя в наличии (оригинал).</t>
+        </is>
+      </c>
+      <c r="I34" s="11" t="inlineStr">
+        <is>
+          <t>Соответствует. Допущено к применению</t>
+        </is>
+      </c>
+      <c r="J34" s="11" t="inlineStr">
+        <is>
+          <t>Иванчук М.В.</t>
+        </is>
+      </c>
+      <c r="K34" s="11" t="inlineStr">
+        <is>
+          <t>ИД листы 2–3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>04.09.2026</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
           <t>Прибор (блок) речевого оповещения, Рупор-300 (поз. AU2)</t>
         </is>
       </c>
-      <c r="D34" s="11" t="inlineStr">
+      <c r="D35" s="11" t="inlineStr">
         <is>
           <t>Болид</t>
         </is>
       </c>
-      <c r="E34" s="10" t="inlineStr">
+      <c r="E35" s="10" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="F34" s="10" t="n">
+      <c r="F35" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="G34" s="11" t="inlineStr">
+      <c r="G35" s="11" t="inlineStr">
         <is>
           <t>Паспорт (руководство по эксплуатации) изготовителя</t>
         </is>
       </c>
-      <c r="H34" s="11" t="inlineStr">
+      <c r="H35" s="11" t="inlineStr">
         <is>
           <t>Внешний осмотр, маркировка, комплектность — без замечаний. Паспорт изготовителя в наличии (оригинал).</t>
         </is>
       </c>
-      <c r="I34" s="11" t="inlineStr">
+      <c r="I35" s="11" t="inlineStr">
         <is>
           <t>Соответствует. Допущено к применению</t>
         </is>
       </c>
-      <c r="J34" s="11" t="inlineStr">
+      <c r="J35" s="11" t="inlineStr">
         <is>
           <t>Иванчук М.В.</t>
         </is>
       </c>
-      <c r="K34" s="11" t="inlineStr">
+      <c r="K35" s="11" t="inlineStr">
         <is>
           <t>ИД листы 2–3</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="12" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
         <is>
           <t>Ответственный за входной контроль (лицо, выполняющее работы)</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="13" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
         <is>
           <t>начальник отдела систем технической безопасности ООО «АльтЭн» Иванчук М.В.</t>
         </is>
       </c>
-      <c r="G37" s="14" t="inlineStr">
+      <c r="G38" s="14" t="inlineStr">
         <is>
           <t>____________________ (подпись)</t>
         </is>
       </c>
-      <c r="I37" s="14" t="inlineStr">
+      <c r="I38" s="14" t="inlineStr">
         <is>
           <t>«____» ____________ 2026 г.</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="12" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
         <is>
           <t>Представитель лица, осуществляющего строительство</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="13" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="13" t="inlineStr">
         <is>
           <t>руководитель проекта Белоногов И.Ю.</t>
         </is>
       </c>
-      <c r="G40" s="14" t="inlineStr">
+      <c r="G41" s="14" t="inlineStr">
         <is>
           <t>____________________ (подпись)</t>
         </is>
       </c>
-      <c r="I40" s="14" t="inlineStr">
+      <c r="I41" s="14" t="inlineStr">
         <is>
           <t>«____» ____________ 2026 г.</t>
         </is>
@@ -1724,25 +1777,25 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A39:K39"/>
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="I41:K41"/>
     <mergeCell ref="A15:K15"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="I37:K37"/>
     <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A36:K36"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A6:K6"/>
+    <mergeCell ref="G38:H38"/>
     <mergeCell ref="A7:K7"/>
     <mergeCell ref="A25:K25"/>
-    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="A37:K37"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="I38:K38"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="I40:K40"/>
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A8:K8"/>
+    <mergeCell ref="G41:H41"/>
     <mergeCell ref="A10:K10"/>
-    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="A40:K40"/>
     <mergeCell ref="A9:K9"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
